--- a/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
@@ -1845,11 +1845,13 @@
       <c r="C3" s="17" t="inlineStr"/>
       <c r="D3" s="17" t="inlineStr"/>
       <c r="E3" s="17" t="inlineStr"/>
-      <c r="F3" s="17" t="inlineStr"/>
+      <c r="F3" s="12" t="n">
+        <v>443452</v>
+      </c>
       <c r="G3" s="17" t="inlineStr"/>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>各月末残高は会計データ/通帳で更新要</t>
+          <t>7月末¥443,452は京信通帳(5枚目・残高整合)より。他月は旧通帳(3/22-6/9)等が必要</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2771,7 +2773,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" s="19" t="inlineStr">
@@ -2780,7 +2782,7 @@
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>50000</v>
+        <v>1100</v>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
@@ -2789,14 +2791,14 @@
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>出金1件・0806905032</t>
+          <t>BB手数料（通帳より追加確認・メール通知外）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
@@ -2805,7 +2807,7 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
@@ -2814,7 +2816,7 @@
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>出金1件・0810918384</t>
+          <t>出金1件・0806905032</t>
         </is>
       </c>
     </row>
@@ -2829,26 +2831,24 @@
           <t>出金</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>未記載</t>
-        </is>
+      <c r="C5" s="12" t="n">
+        <v>200000</v>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>三井住友</t>
+          <t>京都信用金庫</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>振込・依頼人デンシシ…※金額未記載</t>
+          <t>出金1件・0810918384</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
@@ -2856,24 +2856,26 @@
           <t>出金</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
-        <v>180000</v>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>未記載</t>
+        </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>京都信用金庫</t>
+          <t>三井住友</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>山中 役員報酬・0812926926</t>
+          <t>振込・依頼人デンシシ…※金額未記載</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
@@ -2881,31 +2883,29 @@
           <t>出金</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>未記載</t>
-        </is>
+      <c r="C7" s="12" t="n">
+        <v>180000</v>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>三井住友</t>
+          <t>京都信用金庫</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>土壌検査代※金額未記載</t>
+          <t>山中 役員報酬・0812926926</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>入金</t>
+          <t>出金</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2920,19 +2920,19 @@
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>振込入金※金額未記載</t>
+          <t>土壌検査代※金額未記載</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>出金</t>
+          <t>入金</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -2947,14 +2947,14 @@
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>※金額未記載</t>
+          <t>振込入金※金額未記載</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
@@ -2962,33 +2962,35 @@
           <t>出金</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
-        <v>10000</v>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>未記載</t>
+        </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>京都信用金庫</t>
+          <t>三井住友</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>出金1件・0824964860</t>
+          <t>※金額未記載</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>入金</t>
+          <t>出金</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>369050</v>
+        <v>10000</v>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
@@ -2997,7 +2999,7 @@
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>入金1件・0825975230</t>
+          <t>出金1件・0824964860</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3015,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>30140</v>
+        <v>369050</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -3022,7 +3024,7 @@
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>入金1件・0825975561</t>
+          <t>入金1件・0825975230</t>
         </is>
       </c>
     </row>
@@ -3037,19 +3039,17 @@
           <t>入金</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>未記載</t>
-        </is>
+      <c r="C13" s="12" t="n">
+        <v>30140</v>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>三井住友</t>
+          <t>京都信用金庫</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>振込入金※金額未記載</t>
+          <t>入金1件・0825975561</t>
         </is>
       </c>
     </row>
@@ -3064,58 +3064,60 @@
           <t>入金</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
-        <v>9400</v>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>未記載</t>
+        </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>三井住友</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>鈴木久貴様カード決済(税込)</t>
+          <t>振込入金※金額未記載</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>出金</t>
+          <t>入金</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>38800</v>
+        <v>9400</v>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>京都信用金庫</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>出金2件・0827987987</t>
+          <t>鈴木久貴様カード決済(税込)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>入金</t>
+          <t>出金</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>9062</v>
+        <v>38800</v>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
@@ -3124,23 +3126,23 @@
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>Square純受取着金※売上計上済・重複計上せず</t>
+          <t>出金2件・0827987987</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>出金</t>
+          <t>入金</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>50000</v>
+        <v>9062</v>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
@@ -3149,7 +3151,7 @@
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>出金1件・0831003955</t>
+          <t>Square純受取着金※売上計上済・重複計上せず</t>
         </is>
       </c>
     </row>
@@ -3165,14 +3167,39 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>京都信用金庫</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>出金1件・0831003955</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
         <v>10380</v>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>京都信用金庫</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>出金2件・0831010791</t>
         </is>

--- a/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_補助_売上受注" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_補助_入出金8月" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_要確認リスト" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_補助_三井住友明細" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3278,7 +3279,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>地代家賃・役員報酬・他者立替(明日香分等)・銀行引落分・減価償却/繰延資産償却 は会計データから加算要</t>
+          <t>地代家賃・役員報酬・減価償却/繰延資産償却 は会計データから加算要（三井住友分は08シートに科目付で取込済）</t>
         </is>
       </c>
     </row>
@@ -3297,24 +3298,24 @@
     <row r="7">
       <c r="A7" s="21" t="inlineStr">
         <is>
-          <t>入出金 4〜7月</t>
+          <t>京信 入出金 4〜6月</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>京信 第二期通帳(3/22〜7/20)はスキャン画像で数値未抽出。銀行帳xlsx/通帳から要転記</t>
+          <t>京信 旧通帳(3/22〜6/9)＝スキャン画像で数値未抽出。7月末残¥443,452は通帳確認済。CSV/明細で4〜6月を要数値化</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t>三井住友銀行</t>
+          <t>三井住友『未確定勘定』の用途</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>通知メールに金額記載なし(8/10,8/18,8/19,8/21,8/25)。Web21明細で金額確定要</t>
+          <t>6月 出10万(W21ﾕ)ｶｹﾊｼ)、7月 出69.19万・入155.0万等が『未確定勘定』のまま。相手先・用途(売上/借入/出資/立替回収)の特定要</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3339,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>売掛金・未収入金・仮払金・未払金・預り金・仮受金の各月末残は会計データで更新要</t>
+          <t>売掛金・未収入金・仮払金(三井住友 7月+52.7万/8月+3.6万 イトウアスカ)・未払金等の各月末残は会計データで更新要</t>
         </is>
       </c>
     </row>
@@ -3360,4 +3361,1203 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>三井住友銀行 普通預金 明細（勘定科目付・6/17〜8/3）</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="8" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>伝票No</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>勘定科目</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>補助科目</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>入金</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>出金</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>残高</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>179</v>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>現金</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr"/>
+      <c r="E3" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F3" s="12" t="inlineStr"/>
+      <c r="G3" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr"/>
+      <c r="E4" s="12" t="inlineStr"/>
+      <c r="F4" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>W21 ﾕ)ｶｹﾊｼ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>181</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr"/>
+      <c r="E5" s="12" t="inlineStr"/>
+      <c r="F5" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>182</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr"/>
+      <c r="E6" s="12" t="inlineStr"/>
+      <c r="F6" s="12" t="n">
+        <v>430</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>-575</v>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>183</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr"/>
+      <c r="E7" s="12" t="inlineStr"/>
+      <c r="F7" s="12" t="n">
+        <v>430</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>-1005</v>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>184</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr"/>
+      <c r="E8" s="12" t="inlineStr"/>
+      <c r="F8" s="12" t="n">
+        <v>430</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>-1435</v>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>185</v>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr"/>
+      <c r="E9" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="12" t="n">
+        <v>-1290</v>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>186</v>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr"/>
+      <c r="E10" s="12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="12" t="n">
+        <v>48710</v>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>187</v>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr"/>
+      <c r="E11" s="12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="12" t="n">
+        <v>548710</v>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ｾﾌﾞﾝBK05KJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>188</v>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr"/>
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="12" t="n">
+        <v>330</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>548380</v>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>ｶ-ﾄﾞﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>189</v>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr"/>
+      <c r="E13" s="12" t="inlineStr"/>
+      <c r="F13" s="12" t="n">
+        <v>90300</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>458080</v>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>W21 ﾕ)ｶｹﾊｼ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>190</v>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>457935</v>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>191</v>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>支払報酬料</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="n">
+        <v>149685</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>308250</v>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>W21 ﾂｼﾞ ﾏｻｼ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>192</v>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr"/>
+      <c r="E16" s="12" t="inlineStr"/>
+      <c r="F16" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>308105</v>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>193</v>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr"/>
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="n">
+        <v>70000</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>238105</v>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>W21 ﾐﾗﾊﾟ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>194</v>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr"/>
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>237960</v>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>195</v>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr"/>
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="n">
+        <v>6600</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>231360</v>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>W21 ﾄﾞ)ﾄﾞｼﾞﾖｳｼﾝﾀﾞﾝﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>196</v>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr"/>
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>231215</v>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>197</v>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr"/>
+      <c r="E21" s="12" t="inlineStr"/>
+      <c r="F21" s="12" t="n">
+        <v>13120</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>218095</v>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>198</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="12" t="n">
+        <v>11077</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>207018</v>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>199</v>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="n">
+        <v>5909</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>201109</v>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr"/>
+      <c r="F24" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>191109</v>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>201</v>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr"/>
+      <c r="E25" s="12" t="inlineStr"/>
+      <c r="F25" s="12" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>189149</v>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>202</v>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr"/>
+      <c r="E26" s="12" t="inlineStr"/>
+      <c r="F26" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>39149</v>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｺｳﾍﾞﾁｻﾞｲｺﾞｳﾄﾞｳｼﾞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>203</v>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr"/>
+      <c r="E27" s="12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F27" s="12" t="inlineStr"/>
+      <c r="G27" s="12" t="n">
+        <v>539149</v>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>204</v>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr"/>
+      <c r="E28" s="12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F28" s="12" t="inlineStr"/>
+      <c r="G28" s="12" t="n">
+        <v>1039149</v>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>205</v>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr"/>
+      <c r="F29" s="12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>839149</v>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>206</v>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr"/>
+      <c r="E30" s="12" t="inlineStr"/>
+      <c r="F30" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>839004</v>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>207</v>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr"/>
+      <c r="F31" s="12" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>539004</v>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>208</v>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr"/>
+      <c r="E32" s="12" t="inlineStr"/>
+      <c r="F32" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>538859</v>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>209</v>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr"/>
+      <c r="E33" s="12" t="inlineStr"/>
+      <c r="F33" s="12" t="n">
+        <v>275000</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>263859</v>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｶ.ｱﾙｹﾐｱｺﾈｸﾄ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>210</v>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr"/>
+      <c r="E34" s="12" t="inlineStr"/>
+      <c r="F34" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>263714</v>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>211</v>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr"/>
+      <c r="E35" s="12" t="inlineStr"/>
+      <c r="F35" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>163714</v>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｶ.ｷｼﾕｳﾌﾟﾗﾂﾄﾌｵ-ﾑ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="n">
+        <v>212</v>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr"/>
+      <c r="E36" s="12" t="inlineStr"/>
+      <c r="F36" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>163569</v>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="n">
+        <v>213</v>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr"/>
+      <c r="F37" s="12" t="n">
+        <v>36000</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>127569</v>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="n">
+        <v>214</v>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr"/>
+      <c r="E38" s="12" t="inlineStr"/>
+      <c r="F38" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>127424</v>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>月別集計</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>入金計</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>出金計</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>101005</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>入金計</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>出金計</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>1550145</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>1385571</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>入金計</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>出金計</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>36145</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_三井住友明細(勘定科目付)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_立替経費(4-6月)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_売上受注(参考)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_要確認(未確定勘定)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_未確定→区分反映" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -191,7 +191,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -972,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1051,7 +1051,7 @@
         <v>35320</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>199855</v>
+        <v>299855</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>93065</v>
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>368491</v>
+        <v>468491</v>
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>支払報酬料</t>
+          <t>販売手数料</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
@@ -1382,174 +1382,252 @@
         <v>0</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0</v>
+        <v>18942</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>149685</v>
+        <v>39600</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>149685</v>
+        <v>58542</v>
       </c>
       <c r="H15" s="15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
+          <t>業務委託費</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>研究開発費</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>6600</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>6600</v>
+      </c>
+      <c r="H17" s="15" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>支払報酬料</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>571885</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>571885</v>
+      </c>
+      <c r="H18" s="15" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B19" s="11" t="n">
         <v>13240</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C19" s="11" t="n">
         <v>5880</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D19" s="11" t="n">
         <v>3585</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E19" s="11" t="n">
         <v>9310</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F19" s="11" t="n">
         <v>1245</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G19" s="13" t="n">
         <v>33260</v>
       </c>
-      <c r="H16" s="15" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>販管費 合計</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B20" s="11" t="n">
         <v>207809</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C20" s="11" t="n">
         <v>238840</v>
       </c>
-      <c r="D17" s="11" t="n">
-        <v>91457</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>396613</v>
-      </c>
-      <c r="F17" s="11" t="n">
+      <c r="D20" s="11" t="n">
+        <v>110399</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>935013</v>
+      </c>
+      <c r="F20" s="11" t="n">
         <v>1245</v>
       </c>
-      <c r="G17" s="13" t="n">
-        <v>935964</v>
-      </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="G20" s="13" t="n">
+        <v>1493306</v>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>確定分の合計（未確定勘定・売上原価・地代家賃・役員報酬・減価償却等は含まず）</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>営業損益（参考）</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B21" s="11" t="n">
         <v>-172489</v>
       </c>
-      <c r="C18" s="11" t="n">
-        <v>-38985</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>1608</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>-356362</v>
-      </c>
-      <c r="F18" s="11" t="n">
+      <c r="C21" s="11" t="n">
+        <v>61015</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>-17334</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>-894762</v>
+      </c>
+      <c r="F21" s="11" t="n">
         <v>-1245</v>
       </c>
-      <c r="G18" s="13" t="n">
-        <v>-567473</v>
-      </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="G21" s="13" t="n">
+        <v>-1024815</v>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>売上高−販管費(確定分)。※未確定勘定・売上原価等 未反映のため暫定</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>【保留：未確定勘定（要・用途分類）】</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>未確定勘定 入金</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>1006526</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>4786165</v>
-      </c>
-      <c r="F20" s="11" t="n">
+      <c r="B23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="13" t="n">
-        <v>5922691</v>
-      </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="C23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>550165</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>550165</v>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
         <is>
           <t>売上/借入/出資/立替回収 等の区分未定（08参照）</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>未確定勘定 出金</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="11" t="n">
-        <v>128942</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>1003700</v>
-      </c>
-      <c r="F21" s="11" t="n">
+      <c r="D24" s="11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="13" t="n">
-        <v>1132642</v>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="F24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
         <is>
           <t>用途未定（08参照）</t>
         </is>
@@ -1558,7 +1636,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1571,7 +1649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1873,7 +1951,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>【参考：当期発生フロー（銀行タグ）】</t>
+          <t>【参考：当期発生フロー（区分反映後）】</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
@@ -1901,21 +1979,21 @@
         <v>1190000</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>2878986</v>
+        <v>2978986</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>36000</v>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>フロー(発生額)。残高は精算反映後に確定</t>
+          <t>立替等の前渡。精算で減少</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>資本金 入金</t>
+          <t>資本金 入金(京信タグ)</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr"/>
@@ -1936,35 +2014,203 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>フロー(発生額)。残高は精算反映後に確定</t>
+          <t>京信『資本金』タグ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>売上高 入金</t>
+          <t>出資金 入金(区分反映)</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr"/>
       <c r="C17" s="11" t="n">
-        <v>35320</v>
+        <v>30000</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>199855</v>
+        <v>0</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>93065</v>
+        <v>360000</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>40251</v>
+        <v>36000</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>フロー(発生額)。残高は精算反映後に確定</t>
+          <t>未確定→出資金と判定分(現金増資)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>借入金 入金</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>オダミノル30万＋CB6 200万</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>仮受金 入金</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr"/>
+      <c r="C19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>900000</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>アカホリ50万＋CB6分70万＋20万</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>買掛金 支払</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr"/>
+      <c r="C20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>365300</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>ﾕ)ｶｹﾊｼ・アルケミア 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>三井住友へ振替</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr"/>
+      <c r="C21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>内部振替(損益・純資産に影響なし)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>消費税還付金</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr"/>
+      <c r="C22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>146526</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>還付入金(未収消費税の回収/雑収入)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>売上高 入金</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="11" t="n">
+        <v>35320</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>299855</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>93065</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>40251</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>銀行『売上高』＋カ)ルフレ100,000</t>
         </is>
       </c>
     </row>
@@ -8849,26 +9095,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>未確定勘定（相手先・用途の特定が必要）＋その他確認事項</t>
+          <t>未確定勘定 → 区分反映結果（俊さん記入シートより）</t>
         </is>
       </c>
       <c r="B1" s="6" t="n"/>
       <c r="C1" s="6" t="n"/>
       <c r="D1" s="6" t="n"/>
-      <c r="E1" s="7" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="7" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
@@ -8883,17 +9131,22 @@
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
+          <t>入出金</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>摘要</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>区分(ご記入欄)</t>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>区分（反映後）</t>
         </is>
       </c>
     </row>
@@ -8908,17 +9161,24 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>＋30,000</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>振込 ヨシダ ナオミ</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr"/>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>出資金(資本金)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
@@ -8931,17 +9191,24 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>＋100,000</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>振込 カ)ルフレ</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr"/>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>売上高</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
@@ -8954,17 +9221,24 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>-7,579</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>7579</v>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr"/>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>販売手数料(マージン)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -8977,17 +9251,24 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>-2,970</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>2970</v>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr"/>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>販売手数料(マージン)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
@@ -9000,17 +9281,24 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>-4,400</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>4400</v>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr"/>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>販売手数料(マージン)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
@@ -9023,17 +9311,24 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>-3,993</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>3993</v>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr"/>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>販売手数料(マージン)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
@@ -9046,17 +9341,24 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>-10,000</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>FB</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>★未記入(要確認)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
@@ -9069,45 +9371,59 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>＋146,526</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>146526</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>還付金</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>消費税還付金</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>京信</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>＋500,000</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>振込 アカホリ ケイスケ</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr"/>
+          <t>三井住友</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>W21 ﾕ)ｶｹﾊｼ</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>買掛金 支払</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
@@ -9115,22 +9431,29 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>＋300,000</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>振込 カメイシ ミツアキ</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr"/>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>振込 アカホリ ケイスケ</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>仮受金</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
@@ -9138,22 +9461,29 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>＋30,000</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>振込 コダマ ショウイチ</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>(振込)</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>出資金(資本金)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
@@ -9161,22 +9491,29 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>＋30,000</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>振込 ヨシダ マスミ</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr"/>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>振込 コダマ ショウイチ</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>出資金(資本金)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" s="18" t="inlineStr">
@@ -9184,22 +9521,29 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>＋36,000</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>振込 サイトウ コウタ</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>振込 ヨシダ マスミ</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>出資金(資本金)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
@@ -9207,45 +9551,59 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>＋300,000</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>ﾌﾘｺﾐ ｵﾀﾞ ﾐﾉﾙ</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr"/>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>振込 サイトウ コウタ</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>出資金(資本金)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>京信</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>-272,200</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>ﾌﾘｺﾐｼﾊﾗｲ ﾖｼﾀﾞ ﾁｶｼ</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr"/>
+          <t>三井住友</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐ</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>★未記入(要確認)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
@@ -9253,22 +9611,29 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>＋2,700,000</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>ﾌﾘｺﾐ ｱｶﾎﾘ ｹｲｽｹ</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr"/>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐ ｵﾀﾞ ﾐﾉﾙ</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>借入金</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
@@ -9276,17 +9641,24 @@
           <t>京信</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>＋200,000</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>ﾌﾘｺﾐ ｱｶﾎﾘ ｹｲｽｹ</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>272200</v>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>ﾖｼﾀﾞ ﾁｶｼ</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>支払報酬料(司法書士)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
@@ -9296,20 +9668,27 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>京信</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>＋20</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>ﾌﾘｺﾐ ｱｶﾎﾘ ｹｲｽｹ</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr"/>
+          <t>三井住友</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐ</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>★未記入(要確認)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
@@ -9319,25 +9698,32 @@
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>京信</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>-39,600</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>FB ｶ) ﾙﾌﾚ</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr"/>
+          <t>三井住友</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>ｾﾌﾞﾝBK05KJ</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>★未記入(要確認)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
@@ -9345,40 +9731,54 @@
           <t>三井住友</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>90300</v>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>W21 ﾕ)ｶｹﾊｼ</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr"/>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>買掛金 支払</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
-          <t>三井住友</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>＋145</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>ﾌﾘｺﾐ</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr"/>
+          <t>京信</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>アカホリ ケイスケ</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>借入金(CB6)200万＋仮受金70万</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
@@ -9388,20 +9788,27 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>三井住友</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>＋50,000</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>ﾌﾘｺﾐ</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr"/>
+          <t>京信</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>アカホリ ケイスケ</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>仮受金</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
@@ -9411,20 +9818,27 @@
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>三井住友</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>＋500,000</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ｾﾌﾞﾝBK05KJ</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr"/>
+          <t>京信</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>アカホリ ケイスケ</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>★未記入(要確認)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
@@ -9434,20 +9848,27 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>三井住友</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>-90,300</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>W21 ﾕ)ｶｹﾊｼ</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr"/>
+          <t>京信</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>39600</v>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>FB カ)ルフレ</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>販売手数料(マージン)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
@@ -9460,17 +9881,24 @@
           <t>三井住友</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>-70,000</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>W21 ﾐﾗﾊﾟ</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr"/>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>業務委託費(情報共有料)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
@@ -9483,17 +9911,24 @@
           <t>三井住友</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>-6,600</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>W21 ﾄﾞ)ﾄﾞｼﾞﾖｳｼﾝﾀﾞﾝﾖｳ</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr"/>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>ﾄﾞｼﾞﾖｳｼﾝﾀﾞﾝ</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>研究開発費</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
@@ -9506,17 +9941,24 @@
           <t>三井住友</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>-150,000</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>W21 ｺｳﾍﾞﾁｻﾞｲｺﾞｳﾄﾞｳｼﾞ</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>ｺｳﾍﾞﾁｻﾞｲ</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>支払報酬料(弁理士)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
@@ -9529,17 +9971,24 @@
           <t>三井住友</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>＋500,000</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr"/>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>ENET069730</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>三井住友へ振替</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
@@ -9552,17 +10001,24 @@
           <t>三井住友</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>＋500,000</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>入</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>ENET069730</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>三井住友へ振替</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
@@ -9575,17 +10031,24 @@
           <t>三井住友</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>-275,000</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>W21 ｶ.ｱﾙｹﾐｱｺﾈｸﾄ</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr"/>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>275000</v>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>ｱﾙｹﾐｱｺﾈｸﾄ</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>買掛金 支払</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
@@ -9598,93 +10061,119 @@
           <t>三井住友</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>W21 ｶ.ｷｼﾕｳﾌﾟﾗﾂﾄﾌｵ-ﾑ</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>ｷｼﾕｳﾌﾟﾗﾂﾄﾌｵ-ﾑ</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>その他の要確認</t>
+          <t>残・未記入（5件）と その他の要確認</t>
         </is>
       </c>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="6" t="n"/>
-      <c r="E35" s="7" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>売上原価(商品棚卸・仕入)：各月末棚卸表が必要</t>
+          <t>未記入5件：6/9京信 出10,000／7/17三井住友 入145／7/23三井住友 入50,000／7/23三井住友 入500,000(セブンBK)／7/23京信 入20</t>
         </is>
       </c>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="6" t="n"/>
-      <c r="E36" s="7" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>地代家賃・役員報酬・減価償却/繰延資産償却：会計データから加算要</t>
+          <t>売上原価(商品棚卸・仕入)：各月末棚卸表が必要</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n"/>
-      <c r="E37" s="7" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>現金及び預金：月末は京信のみ。三井住友・現金・他口座の月末残を合算要</t>
+          <t>地代家賃・役員報酬・減価償却/繰延資産償却：会計データから加算要</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="6" t="n"/>
-      <c r="E38" s="7" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>立替経費(山中)：7・8月のレシート未取込</t>
+          <t>現金及び預金：月末は京信のみ。三井住友・現金・他口座の月末残を合算要</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="6" t="n"/>
-      <c r="E39" s="7" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>資本金：4月 京信入金3,000,000(現金増資)＋現物出資(4/20 8,400,000・4/30 4,230,000)の反映要</t>
+          <t>立替経費(山中)：7・8月のレシート未取込</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
-      <c r="E40" s="7" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>資本金：現金増資(京信タグ3,000,000＋区分反映426,000)＋現物出資(4/20 8,400,000・4/30 4,230,000)の整理要</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A40:E40"/>
+  <mergeCells count="8">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
@@ -185,8 +185,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -972,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1072,179 +1072,163 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>【販売費及び一般管理費（京信＋三井住友＋立替 合算）】</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="7" t="n"/>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>売上原価（内職代・振込）</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr"/>
+      <c r="C4" s="16" t="inlineStr"/>
+      <c r="D4" s="16" t="inlineStr"/>
+      <c r="E4" s="16" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>内職代の振込先の特定要（該当振込を集計）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>旅費交通費</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>82200</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>56862</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>38428</v>
-      </c>
-      <c r="E5" s="11" t="n">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>売上総利益</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr"/>
+      <c r="C5" s="16" t="inlineStr"/>
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="16" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>177490</v>
-      </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>立替は4〜6月のみ</t>
+          <t>売上高−売上原価（原価確定後）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>会議費・接待費</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>56211</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>92451</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>20084</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>168746</v>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>立替は4〜6月のみ</t>
-        </is>
-      </c>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>【販売費及び一般管理費（両行＋立替＋方針計上）】</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>消耗品費</t>
+          <t>役員報酬</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>13548</v>
+        <v>700000</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>59117</v>
+        <v>700000</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>9700</v>
+        <v>700000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>82365</v>
+        <v>3500000</v>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>立替は4〜6月のみ</t>
+          <t>方針計上 山中40万＋伊藤明日香30万＝70万/月</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>地代家賃</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>11710</v>
+        <v>200000</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>860</v>
+        <v>200000</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>15510</v>
+        <v>200000</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>28080</v>
-      </c>
-      <c r="H8" s="15" t="inlineStr"/>
+        <v>1000000</v>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>方針計上 20万/月(月末)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>荷造運賃</t>
+          <t>旅費交通費</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>0</v>
+        <v>382200</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1530</v>
+        <v>356862</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0</v>
+        <v>338428</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1530</v>
+        <v>1677490</v>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>立替は4〜6月のみ</t>
+          <t>方針30万/月(阪・池島・伊藤友隆 各10万枠)＋山中立替(4〜6月)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>保険料</t>
+          <t>会議費・接待費</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>12100</v>
+        <v>56211</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0</v>
+        <v>92451</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0</v>
+        <v>20084</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>0</v>
@@ -1253,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>12100</v>
+        <v>168746</v>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
@@ -1264,93 +1248,97 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>諸会費</t>
+          <t>消耗品費</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>10000</v>
+        <v>13548</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>12000</v>
+        <v>59117</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>10000</v>
+        <v>9700</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>42000</v>
-      </c>
-      <c r="H11" s="15" t="inlineStr"/>
+        <v>82365</v>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>立替は4〜6月のみ</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>雑費</t>
+          <t>通信費</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
+        <v>11710</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>2200</v>
-      </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0</v>
+        <v>15510</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>立替は4〜6月のみ</t>
-        </is>
-      </c>
+        <v>28080</v>
+      </c>
+      <c r="H12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>広告宣伝費</t>
+          <t>荷造運賃</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>8800</v>
+        <v>1530</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>8800</v>
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>35200</v>
-      </c>
-      <c r="H13" s="15" t="inlineStr"/>
+        <v>1530</v>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>立替は4〜6月のみ</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>外注費</t>
+          <t>保険料</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>0</v>
@@ -1359,98 +1347,106 @@
         <v>0</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>203308</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>203308</v>
-      </c>
-      <c r="H14" s="15" t="inlineStr"/>
+        <v>12100</v>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>立替は4〜6月のみ</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>販売手数料</t>
+          <t>諸会費</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>18942</v>
+        <v>10000</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>39600</v>
+        <v>10000</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>58542</v>
+        <v>42000</v>
       </c>
       <c r="H15" s="15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>業務委託費</t>
+          <t>雑費</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>70000</v>
-      </c>
-      <c r="H16" s="15" t="inlineStr"/>
+        <v>2200</v>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>立替は4〜6月のみ</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>研究開発費</t>
+          <t>広告宣伝費</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>6600</v>
+        <v>8800</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>6600</v>
+        <v>35200</v>
       </c>
       <c r="H17" s="15" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>支払報酬料</t>
+          <t>外注費</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
@@ -1463,171 +1459,275 @@
         <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>571885</v>
+        <v>203308</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>571885</v>
+        <v>203308</v>
       </c>
       <c r="H18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>支払手数料</t>
+          <t>販売手数料</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>13240</v>
+        <v>0</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5880</v>
+        <v>0</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>3585</v>
+        <v>18942</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>9310</v>
+        <v>39600</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1245</v>
+        <v>0</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>33260</v>
+        <v>58542</v>
       </c>
       <c r="H19" s="15" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>販管費 合計</t>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>業務委託費</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>207809</v>
+        <v>0</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>238840</v>
+        <v>0</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>110399</v>
+        <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>935013</v>
+        <v>70000</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1245</v>
+        <v>0</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>1493306</v>
-      </c>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>確定分の合計（未確定勘定・売上原価・地代家賃・役員報酬・減価償却等は含まず）</t>
-        </is>
-      </c>
+        <v>70000</v>
+      </c>
+      <c r="H20" s="15" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>営業損益（参考）</t>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>研究開発費</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>-172489</v>
+        <v>0</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>61015</v>
+        <v>0</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>-17334</v>
+        <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>-894762</v>
+        <v>6600</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>-1245</v>
+        <v>0</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>-1024815</v>
-      </c>
-      <c r="H21" s="15" t="inlineStr">
-        <is>
-          <t>売上高−販管費(確定分)。※未確定勘定・売上原価等 未反映のため暫定</t>
-        </is>
-      </c>
+        <v>6600</v>
+      </c>
+      <c r="H21" s="15" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>【保留：未確定勘定（要・用途分類）】</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="7" t="n"/>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>支払報酬料</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>571885</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>571885</v>
+      </c>
+      <c r="H22" s="15" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>13240</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>3585</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>9310</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>1245</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>33260</v>
+      </c>
+      <c r="H23" s="15" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>販管費 合計</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>1407809</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>1438840</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>1310399</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>2135013</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>1201245</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>7493306</v>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>両行＋立替＋方針計上(役員報酬・地代家賃・旅費枠)。減価償却/繰延資産償却は0(前期繰延償却は第1期で終了と推定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>営業損益（参考）</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>-1372489</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>-1138985</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>-1217334</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>-2094762</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>-1201245</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>-7024815</v>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>売上総利益−販管費。※売上原価(内職代)・未確定勘定 未反映のため暫定</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>【保留：未確定勘定（要・用途分類）】</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
           <t>未確定勘定 入金</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E27" s="11" t="n">
         <v>550165</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G27" s="13" t="n">
         <v>550165</v>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="H27" s="15" t="inlineStr">
         <is>
           <t>売上/借入/出資/立替回収 等の区分未定（08参照）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>未確定勘定 出金</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D28" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G28" s="13" t="n">
         <v>10000</v>
       </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="H28" s="15" t="inlineStr">
         <is>
           <t>用途未定（08参照）</t>
         </is>
@@ -1635,8 +1735,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A6:H6"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1757,11 +1857,11 @@
       <c r="B4" s="11" t="n">
         <v>836000</v>
       </c>
-      <c r="C4" s="17" t="inlineStr"/>
-      <c r="D4" s="17" t="inlineStr"/>
-      <c r="E4" s="17" t="inlineStr"/>
-      <c r="F4" s="17" t="inlineStr"/>
-      <c r="G4" s="17" t="inlineStr"/>
+      <c r="C4" s="16" t="inlineStr"/>
+      <c r="D4" s="16" t="inlineStr"/>
+      <c r="E4" s="16" t="inlineStr"/>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr"/>
       <c r="H4" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -1777,11 +1877,11 @@
       <c r="B5" s="11" t="n">
         <v>2540000</v>
       </c>
-      <c r="C5" s="17" t="inlineStr"/>
-      <c r="D5" s="17" t="inlineStr"/>
-      <c r="E5" s="17" t="inlineStr"/>
-      <c r="F5" s="17" t="inlineStr"/>
-      <c r="G5" s="17" t="inlineStr"/>
+      <c r="C5" s="16" t="inlineStr"/>
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="16" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr"/>
+      <c r="G5" s="16" t="inlineStr"/>
       <c r="H5" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -1797,11 +1897,11 @@
       <c r="B6" s="11" t="n">
         <v>146526</v>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
+      <c r="C6" s="16" t="inlineStr"/>
+      <c r="D6" s="16" t="inlineStr"/>
+      <c r="E6" s="16" t="inlineStr"/>
+      <c r="F6" s="16" t="inlineStr"/>
+      <c r="G6" s="16" t="inlineStr"/>
       <c r="H6" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -1817,11 +1917,11 @@
       <c r="B7" s="11" t="n">
         <v>2286511</v>
       </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
+      <c r="C7" s="16" t="inlineStr"/>
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="16" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr"/>
       <c r="H7" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -1837,11 +1937,11 @@
       <c r="B8" s="11" t="n">
         <v>416675</v>
       </c>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
+      <c r="C8" s="16" t="inlineStr"/>
+      <c r="D8" s="16" t="inlineStr"/>
+      <c r="E8" s="16" t="inlineStr"/>
+      <c r="F8" s="16" t="inlineStr"/>
+      <c r="G8" s="16" t="inlineStr"/>
       <c r="H8" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -1857,11 +1957,11 @@
       <c r="B9" s="11" t="n">
         <v>1239309</v>
       </c>
-      <c r="C9" s="17" t="inlineStr"/>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
+      <c r="C9" s="16" t="inlineStr"/>
+      <c r="D9" s="16" t="inlineStr"/>
+      <c r="E9" s="16" t="inlineStr"/>
+      <c r="F9" s="16" t="inlineStr"/>
+      <c r="G9" s="16" t="inlineStr"/>
       <c r="H9" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -1877,11 +1977,11 @@
       <c r="B10" s="11" t="n">
         <v>5207</v>
       </c>
-      <c r="C10" s="17" t="inlineStr"/>
-      <c r="D10" s="17" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
+      <c r="C10" s="16" t="inlineStr"/>
+      <c r="D10" s="16" t="inlineStr"/>
+      <c r="E10" s="16" t="inlineStr"/>
+      <c r="F10" s="16" t="inlineStr"/>
+      <c r="G10" s="16" t="inlineStr"/>
       <c r="H10" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -1897,11 +1997,11 @@
       <c r="B11" s="11" t="n">
         <v>100000</v>
       </c>
-      <c r="C11" s="17" t="inlineStr"/>
-      <c r="D11" s="17" t="inlineStr"/>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
+      <c r="C11" s="16" t="inlineStr"/>
+      <c r="D11" s="16" t="inlineStr"/>
+      <c r="E11" s="16" t="inlineStr"/>
+      <c r="F11" s="16" t="inlineStr"/>
+      <c r="G11" s="16" t="inlineStr"/>
       <c r="H11" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -1917,11 +2017,11 @@
       <c r="B12" s="11" t="n">
         <v>9600000</v>
       </c>
-      <c r="C12" s="17" t="inlineStr"/>
-      <c r="D12" s="17" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
+      <c r="C12" s="16" t="inlineStr"/>
+      <c r="D12" s="16" t="inlineStr"/>
+      <c r="E12" s="16" t="inlineStr"/>
+      <c r="F12" s="16" t="inlineStr"/>
+      <c r="G12" s="16" t="inlineStr"/>
       <c r="H12" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -1937,11 +2037,11 @@
       <c r="B13" s="11" t="n">
         <v>-4295410</v>
       </c>
-      <c r="C13" s="17" t="inlineStr"/>
-      <c r="D13" s="17" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr"/>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
+      <c r="C13" s="16" t="inlineStr"/>
+      <c r="D13" s="16" t="inlineStr"/>
+      <c r="E13" s="16" t="inlineStr"/>
+      <c r="F13" s="16" t="inlineStr"/>
+      <c r="G13" s="16" t="inlineStr"/>
       <c r="H13" s="15" t="inlineStr">
         <is>
           <t>会計データで更新要</t>
@@ -3007,7 +3107,7 @@
       <c r="B27" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -4355,7 +4455,7 @@
       <c r="B73" s="18" t="n">
         <v>71</v>
       </c>
-      <c r="C73" s="17" t="inlineStr">
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -4619,7 +4719,7 @@
       <c r="B82" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="C82" s="17" t="inlineStr">
+      <c r="C82" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -4675,7 +4775,7 @@
       <c r="B84" s="18" t="n">
         <v>82</v>
       </c>
-      <c r="C84" s="17" t="inlineStr">
+      <c r="C84" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -4731,7 +4831,7 @@
       <c r="B86" s="18" t="n">
         <v>84</v>
       </c>
-      <c r="C86" s="17" t="inlineStr">
+      <c r="C86" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -4787,7 +4887,7 @@
       <c r="B88" s="18" t="n">
         <v>86</v>
       </c>
-      <c r="C88" s="17" t="inlineStr">
+      <c r="C88" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -4843,7 +4943,7 @@
       <c r="B90" s="18" t="n">
         <v>88</v>
       </c>
-      <c r="C90" s="17" t="inlineStr">
+      <c r="C90" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -4927,7 +5027,7 @@
       <c r="B93" s="18" t="n">
         <v>91</v>
       </c>
-      <c r="C93" s="17" t="inlineStr">
+      <c r="C93" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -5251,7 +5351,7 @@
       <c r="B104" s="18" t="n">
         <v>102</v>
       </c>
-      <c r="C104" s="17" t="inlineStr">
+      <c r="C104" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -5459,7 +5559,7 @@
       <c r="B111" s="18" t="n">
         <v>109</v>
       </c>
-      <c r="C111" s="17" t="inlineStr">
+      <c r="C111" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -5607,7 +5707,7 @@
       <c r="B116" s="18" t="n">
         <v>114</v>
       </c>
-      <c r="C116" s="17" t="inlineStr">
+      <c r="C116" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -5727,7 +5827,7 @@
       <c r="B120" s="18" t="n">
         <v>118</v>
       </c>
-      <c r="C120" s="17" t="inlineStr">
+      <c r="C120" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -5931,7 +6031,7 @@
       <c r="B127" s="18" t="n">
         <v>125</v>
       </c>
-      <c r="C127" s="17" t="inlineStr">
+      <c r="C127" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -6195,7 +6295,7 @@
       <c r="B136" s="18" t="n">
         <v>134</v>
       </c>
-      <c r="C136" s="17" t="inlineStr">
+      <c r="C136" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -6223,7 +6323,7 @@
       <c r="B137" s="18" t="n">
         <v>135</v>
       </c>
-      <c r="C137" s="17" t="inlineStr">
+      <c r="C137" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -6339,7 +6439,7 @@
       <c r="B141" s="18" t="n">
         <v>139</v>
       </c>
-      <c r="C141" s="17" t="inlineStr">
+      <c r="C141" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -6423,7 +6523,7 @@
       <c r="B144" s="18" t="n">
         <v>142</v>
       </c>
-      <c r="C144" s="17" t="inlineStr">
+      <c r="C144" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -6451,7 +6551,7 @@
       <c r="B145" s="18" t="n">
         <v>143</v>
       </c>
-      <c r="C145" s="17" t="inlineStr">
+      <c r="C145" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -7215,7 +7315,7 @@
       <c r="B172" s="18" t="n">
         <v>170</v>
       </c>
-      <c r="C172" s="17" t="inlineStr">
+      <c r="C172" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -7594,7 +7694,7 @@
       <c r="B4" s="18" t="n">
         <v>180</v>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -7734,7 +7834,7 @@
       <c r="B9" s="18" t="n">
         <v>185</v>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -7762,7 +7862,7 @@
       <c r="B10" s="18" t="n">
         <v>186</v>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -7790,7 +7890,7 @@
       <c r="B11" s="18" t="n">
         <v>187</v>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -7846,7 +7946,7 @@
       <c r="B13" s="18" t="n">
         <v>189</v>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -7958,7 +8058,7 @@
       <c r="B17" s="18" t="n">
         <v>193</v>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -8014,7 +8114,7 @@
       <c r="B19" s="18" t="n">
         <v>195</v>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -8222,7 +8322,7 @@
       <c r="B26" s="18" t="n">
         <v>202</v>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -8250,7 +8350,7 @@
       <c r="B27" s="18" t="n">
         <v>203</v>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -8278,7 +8378,7 @@
       <c r="B28" s="18" t="n">
         <v>204</v>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -8426,7 +8526,7 @@
       <c r="B33" s="18" t="n">
         <v>209</v>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -8482,7 +8582,7 @@
       <c r="B35" s="18" t="n">
         <v>211</v>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
@@ -9095,7 +9195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10107,7 +10207,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>売上原価(商品棚卸・仕入)：各月末棚卸表が必要</t>
+          <t>【売上原価=内職代(振込出金)】振込先(氏名)のご指定要。該当振込を各月の売上原価に集計します</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
@@ -10119,7 +10219,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>地代家賃・役員報酬・減価償却/繰延資産償却：会計データから加算要</t>
+          <t>【役員報酬】伊藤明日香の額：ご指示に20万(家賃と併せ40万出金)と30万(役員報酬)の両方あり。計上は30万で反映中→要確認</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
@@ -10131,7 +10231,7 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>現金及び預金：月末は京信のみ。三井住友・現金・他口座の月末残を合算要</t>
+          <t>【方針計上済】役員報酬70万/月・地代家賃20万/月・旅費枠30万/月。実際の出金(仮払金)との精算(前渡→費用振替)は税理士で</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
@@ -10143,7 +10243,7 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>立替経費(山中)：7・8月のレシート未取込</t>
+          <t>【減価償却/繰延資産償却】0で計上(第1期の繰延資産償却1,063,398は第1期で終了と推定)。ソフトウェア残416,675の償却要否のみ税理士確認</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
@@ -10155,7 +10255,7 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>資本金：現金増資(京信タグ3,000,000＋区分反映426,000)＋現物出資(4/20 8,400,000・4/30 4,230,000)の整理要</t>
+          <t>【現預金】京信・三井住友の2行のみ(他口座なし)。三井住友の各月末残の取得要(現状は京信のみ記入)</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
@@ -10164,16 +10264,42 @@
       <c r="E41" s="6" t="n"/>
       <c r="F41" s="7" t="n"/>
     </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>立替経費(山中)：7・8月のレシート未取込</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>資本金：現金増資(京信タグ3,000,000＋区分反映426,000)＋現物出資(4/20 8,400,000・4/30 4,230,000)の整理要</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
@@ -1080,14 +1080,16 @@
       <c r="B4" s="16" t="inlineStr"/>
       <c r="C4" s="16" t="inlineStr"/>
       <c r="D4" s="16" t="inlineStr"/>
-      <c r="E4" s="16" t="inlineStr"/>
+      <c r="E4" s="11" t="n">
+        <v>181528</v>
+      </c>
       <c r="F4" s="16" t="inlineStr"/>
       <c r="G4" s="13" t="n">
-        <v>0</v>
+        <v>181528</v>
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>内職代の振込先の特定要（該当振込を集計）</t>
+          <t>ニイカワ/アサダ/ナカムラ等の個人振込。7月=181,528(11件)。4〜6月は当明細範囲外で要データ</t>
         </is>
       </c>
     </row>
@@ -1100,14 +1102,16 @@
       <c r="B5" s="16" t="inlineStr"/>
       <c r="C5" s="16" t="inlineStr"/>
       <c r="D5" s="16" t="inlineStr"/>
-      <c r="E5" s="16" t="inlineStr"/>
+      <c r="E5" s="11" t="n">
+        <v>-141277</v>
+      </c>
       <c r="F5" s="16" t="inlineStr"/>
       <c r="G5" s="13" t="n">
-        <v>0</v>
+        <v>-141277</v>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>売上高−売上原価（原価確定後）</t>
+          <t>売上高−売上原価（原価判明月のみ）</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10211,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>【売上原価=内職代(振込出金)】振込先(氏名)のご指定要。該当振込を各月の売上原価に集計します</t>
+          <t>【売上原価=内職代】7/23分 181,528円(ニイカワ42,890/アサダ51,160/ナカムラ11,760/アワノ36,300/ダテ/ヤギ×2/ナカゾノ/オカジマ/ケンコウサヌキ)を計上。4〜6月分は当明細(6月末〜9/1)の範囲外で要データ</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
@@ -10219,7 +10223,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>【役員報酬】伊藤明日香の額：ご指示に20万(家賃と併せ40万出金)と30万(役員報酬)の両方あり。計上は30万で反映中→要確認</t>
+          <t>【役員報酬】伊藤明日香30万で確定(俊さん確認済)</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
@@ -10255,7 +10259,7 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>【現預金】京信・三井住友の2行のみ(他口座なし)。三井住友の各月末残の取得要(現状は京信のみ記入)</t>
+          <t>【現預金】京信・三井住友の2行のみ(他口座なし・俊さん確認済)。京信の月末残は確定。三井住友の各月末残の取得要(BS現預金を2行合算で確定するため)</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>

--- a/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
@@ -1081,11 +1081,11 @@
       <c r="C4" s="16" t="inlineStr"/>
       <c r="D4" s="16" t="inlineStr"/>
       <c r="E4" s="11" t="n">
-        <v>181528</v>
+        <v>135750</v>
       </c>
       <c r="F4" s="16" t="inlineStr"/>
       <c r="G4" s="13" t="n">
-        <v>181528</v>
+        <v>135750</v>
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       <c r="C5" s="16" t="inlineStr"/>
       <c r="D5" s="16" t="inlineStr"/>
       <c r="E5" s="11" t="n">
-        <v>-141277</v>
+        <v>-95499</v>
       </c>
       <c r="F5" s="16" t="inlineStr"/>
       <c r="G5" s="13" t="n">
-        <v>-141277</v>
+        <v>-95499</v>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>18942</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>39600</v>
+        <v>85378</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>58542</v>
+        <v>104320</v>
       </c>
       <c r="H19" s="15" t="inlineStr"/>
     </row>
@@ -1619,13 +1619,13 @@
         <v>1310399</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2135013</v>
+        <v>2180791</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>1201245</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>7493306</v>
+        <v>7539084</v>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
@@ -1649,13 +1649,13 @@
         <v>-1217334</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-2094762</v>
+        <v>-2140540</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>-1201245</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>-7024815</v>
+        <v>-7070593</v>
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10211,7 +10211,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>【売上原価=内職代】7/23分 181,528円(ニイカワ42,890/アサダ51,160/ナカムラ11,760/アワノ36,300/ダテ/ヤギ×2/ナカゾノ/オカジマ/ケンコウサヌキ)を計上。4〜6月分は当明細(6月末〜9/1)の範囲外で要データ</t>
+          <t>【売上原価=内職代】7/23分 135,750円(ニイカワ46,190/アサダ51,160/ナカムラ11,760/ダテ6,300/ヤギ×2 11,700/ナカゾノ5,940/オカジマ2,700)を計上。4〜6月分は当明細(6月末〜9/1)範囲外で要データ</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
@@ -10223,7 +10223,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>【役員報酬】伊藤明日香30万で確定(俊さん確認済)</t>
+          <t>【マージン(販売手数料)へ移動】アワノチエ36,300・ケンコウサヌキ9,478(俊さん訂正)。伊藤友隆21,780は出金のため売上ではなく区分保留(要確認)</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
@@ -10235,7 +10235,7 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>【方針計上済】役員報酬70万/月・地代家賃20万/月・旅費枠30万/月。実際の出金(仮払金)との精算(前渡→費用振替)は税理士で</t>
+          <t>【役員報酬】伊藤明日香30万で確定(俊さん確認済)</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
@@ -10247,7 +10247,7 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>【減価償却/繰延資産償却】0で計上(第1期の繰延資産償却1,063,398は第1期で終了と推定)。ソフトウェア残416,675の償却要否のみ税理士確認</t>
+          <t>【方針計上済】役員報酬70万/月・地代家賃20万/月・旅費枠30万/月。実際の出金(仮払金)との精算(前渡→費用振替)は税理士で</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
@@ -10259,7 +10259,7 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>【現預金】京信・三井住友の2行のみ(他口座なし・俊さん確認済)。京信の月末残は確定。三井住友の各月末残の取得要(BS現預金を2行合算で確定するため)</t>
+          <t>【減価償却/繰延資産償却】0で計上(第1期の繰延資産償却1,063,398は第1期で終了と推定)。ソフトウェア残416,675の償却要否のみ税理士確認</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
@@ -10271,7 +10271,7 @@
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>立替経費(山中)：7・8月のレシート未取込</t>
+          <t>【現預金】京信・三井住友の2行のみ(他口座なし・俊さん確認済)。京信の月末残は確定。三井住友の各月末残の取得要(BS現預金を2行合算で確定するため)</t>
         </is>
       </c>
       <c r="B42" s="6" t="n"/>
@@ -10283,7 +10283,7 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>資本金：現金増資(京信タグ3,000,000＋区分反映426,000)＋現物出資(4/20 8,400,000・4/30 4,230,000)の整理要</t>
+          <t>立替経費(山中)：7・8月のレシート未取込</t>
         </is>
       </c>
       <c r="B43" s="6" t="n"/>
@@ -10292,12 +10292,25 @@
       <c r="E43" s="6" t="n"/>
       <c r="F43" s="7" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>資本金：現金増資(京信タグ3,000,000＋区分反映426,000)＋現物出資(4/20 8,400,000・4/30 4,230,000)の整理要</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A42:F42"/>
     <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A40:F40"/>

--- a/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
@@ -1489,13 +1489,13 @@
         <v>18942</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>85378</v>
+        <v>107158</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>104320</v>
+        <v>126100</v>
       </c>
       <c r="H19" s="15" t="inlineStr"/>
     </row>
@@ -1619,13 +1619,13 @@
         <v>1310399</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2180791</v>
+        <v>2202571</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>1201245</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>7539084</v>
+        <v>7560864</v>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
@@ -1649,13 +1649,13 @@
         <v>-1217334</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>-2140540</v>
+        <v>-2162320</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>-1201245</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>-7070593</v>
+        <v>-7092373</v>
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1825,7 +1825,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>現金及び預金（うち京信）</t>
+          <t>現金及び預金（京信＋三井住友）</t>
         </is>
       </c>
       <c r="B3" s="11" t="n">
@@ -1841,65 +1841,81 @@
         <v>60909</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>443452</v>
+        <v>607021</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>311424</v>
+        <v>323397</v>
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>月末は京信残高(通帳一致)。三井住友・現金・他口座は別途合算要</t>
+          <t>2行合算。京信=通帳一致。三井住友=補助簿(口座開設6/17〜/4-5月未開設・6月末≒0)＋8月末Web21実残¥11,973</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>売掛金</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="n">
-        <v>836000</v>
-      </c>
-      <c r="C4" s="16" t="inlineStr"/>
-      <c r="D4" s="16" t="inlineStr"/>
-      <c r="E4" s="16" t="inlineStr"/>
-      <c r="F4" s="16" t="inlineStr"/>
-      <c r="G4" s="16" t="inlineStr"/>
+          <t xml:space="preserve">　うち 京信</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n">
+        <v>1117317</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>102492</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>60909</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>443452</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>311424</v>
+      </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>会計データで更新要</t>
+          <t>通帳一致</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>2540000</v>
-      </c>
-      <c r="C5" s="16" t="inlineStr"/>
-      <c r="D5" s="16" t="inlineStr"/>
-      <c r="E5" s="16" t="inlineStr"/>
-      <c r="F5" s="16" t="inlineStr"/>
-      <c r="G5" s="16" t="inlineStr"/>
+          <t xml:space="preserve">　うち 三井住友</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>163569</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>11973</v>
+      </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>会計データで更新要</t>
+          <t>口座開設6/17〜。6月末は口座ほぼ空(▲1,005/概算0)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>未収入金</t>
+          <t>売掛金</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>146526</v>
+        <v>836000</v>
       </c>
       <c r="C6" s="16" t="inlineStr"/>
       <c r="D6" s="16" t="inlineStr"/>
@@ -1915,11 +1931,11 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>仮払金</t>
+          <t>商品</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>2286511</v>
+        <v>2540000</v>
       </c>
       <c r="C7" s="16" t="inlineStr"/>
       <c r="D7" s="16" t="inlineStr"/>
@@ -1935,11 +1951,11 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>ソフトウェア</t>
+          <t>未収入金</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>416675</v>
+        <v>146526</v>
       </c>
       <c r="C8" s="16" t="inlineStr"/>
       <c r="D8" s="16" t="inlineStr"/>
@@ -1955,11 +1971,11 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>未払金</t>
+          <t>仮払金</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>1239309</v>
+        <v>2286511</v>
       </c>
       <c r="C9" s="16" t="inlineStr"/>
       <c r="D9" s="16" t="inlineStr"/>
@@ -1975,11 +1991,11 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>預り金</t>
+          <t>ソフトウェア</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>5207</v>
+        <v>416675</v>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="16" t="inlineStr"/>
@@ -1995,11 +2011,11 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>仮受金</t>
+          <t>未払金</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>100000</v>
+        <v>1239309</v>
       </c>
       <c r="C11" s="16" t="inlineStr"/>
       <c r="D11" s="16" t="inlineStr"/>
@@ -2015,11 +2031,11 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>資本金</t>
+          <t>預り金</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>9600000</v>
+        <v>5207</v>
       </c>
       <c r="C12" s="16" t="inlineStr"/>
       <c r="D12" s="16" t="inlineStr"/>
@@ -2035,11 +2051,11 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>繰越利益剰余金</t>
+          <t>仮受金</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>-4295410</v>
+        <v>100000</v>
       </c>
       <c r="C13" s="16" t="inlineStr"/>
       <c r="D13" s="16" t="inlineStr"/>
@@ -2053,112 +2069,96 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>【参考：当期発生フロー（区分反映後）】</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>資本金</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>9600000</v>
+      </c>
+      <c r="C14" s="16" t="inlineStr"/>
+      <c r="D14" s="16" t="inlineStr"/>
+      <c r="E14" s="16" t="inlineStr"/>
+      <c r="F14" s="16" t="inlineStr"/>
+      <c r="G14" s="16" t="inlineStr"/>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>会計データで更新要</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>仮払金 支出</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="11" t="n">
-        <v>1920000</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>1190000</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>2978986</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>36000</v>
-      </c>
+          <t>繰越利益剰余金</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>-4295410</v>
+      </c>
+      <c r="C15" s="16" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr"/>
+      <c r="E15" s="16" t="inlineStr"/>
+      <c r="F15" s="16" t="inlineStr"/>
+      <c r="G15" s="16" t="inlineStr"/>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>立替等の前渡。精算で減少</t>
+          <t>会計データで更新要</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>資本金 入金(京信タグ)</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="11" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="15" t="inlineStr">
-        <is>
-          <t>京信『資本金』タグ</t>
-        </is>
-      </c>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>【参考：当期発生フロー（区分反映後）】</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>出資金 入金(区分反映)</t>
+          <t>仮払金 支出</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr"/>
       <c r="C17" s="11" t="n">
-        <v>30000</v>
+        <v>1920000</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0</v>
+        <v>1290000</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>360000</v>
+        <v>1190000</v>
       </c>
       <c r="F17" s="11" t="n">
+        <v>2978986</v>
+      </c>
+      <c r="G17" s="11" t="n">
         <v>36000</v>
       </c>
-      <c r="G17" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>未確定→出資金と判定分(現金増資)</t>
+          <t>立替等の前渡。精算で減少</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>借入金 入金</t>
+          <t>資本金 入金(京信タグ)</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr"/>
       <c r="C18" s="11" t="n">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>0</v>
@@ -2167,49 +2167,49 @@
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2300000</v>
+        <v>0</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>オダミノル30万＋CB6 200万</t>
+          <t>京信『資本金』タグ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>仮受金 入金</t>
+          <t>出資金 入金(区分反映)</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr"/>
       <c r="C19" s="11" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>500000</v>
+        <v>360000</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>900000</v>
+        <v>36000</v>
       </c>
       <c r="G19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>アカホリ50万＋CB6分70万＋20万</t>
+          <t>未確定→出資金と判定分(現金増資)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>買掛金 支払</t>
+          <t>借入金 入金</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr"/>
@@ -2220,24 +2220,24 @@
         <v>0</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>365300</v>
+        <v>2300000</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>ﾕ)ｶｹﾊｼ・アルケミア 等</t>
+          <t>オダミノル30万＋CB6 200万</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>三井住友へ振替</t>
+          <t>仮受金 入金</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr"/>
@@ -2248,24 +2248,24 @@
         <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>内部振替(損益・純資産に影響なし)</t>
+          <t>アカホリ50万＋CB6分70万＋20万</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>消費税還付金</t>
+          <t>買掛金 支払</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr"/>
@@ -2276,51 +2276,107 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>146526</v>
+        <v>100000</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0</v>
+        <v>365300</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>還付入金(未収消費税の回収/雑収入)</t>
+          <t>ﾕ)ｶｹﾊｼ・アルケミア 等</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>売上高 入金</t>
+          <t>三井住友へ振替</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr"/>
       <c r="C23" s="11" t="n">
-        <v>35320</v>
+        <v>0</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>299855</v>
+        <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>93065</v>
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>40251</v>
+        <v>1000000</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
+          <t>内部振替(損益・純資産に影響なし)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>消費税還付金</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr"/>
+      <c r="C24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>146526</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>還付入金(未収消費税の回収/雑収入)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>売上高 入金</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr"/>
+      <c r="C25" s="11" t="n">
+        <v>35320</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>299855</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>93065</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>40251</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
           <t>銀行『売上高』＋カ)ルフレ100,000</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9199,7 +9255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10211,7 +10267,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>【売上原価=内職代】7/23分 135,750円(ニイカワ46,190/アサダ51,160/ナカムラ11,760/ダテ6,300/ヤギ×2 11,700/ナカゾノ5,940/オカジマ2,700)を計上。4〜6月分は当明細(6月末〜9/1)範囲外で要データ</t>
+          <t>【売上原価=内職代】7月 135,750円(ニイカワ46,190/アサダ51,160/ナカムラ11,760/ダテ6,300/ヤギ×2 11,700/ナカゾノ5,940/オカジマ2,700)。4〜6月は両行に該当出金なし=未発生(俊さん確認)</t>
         </is>
       </c>
       <c r="B37" s="6" t="n"/>
@@ -10223,7 +10279,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>【マージン(販売手数料)へ移動】アワノチエ36,300・ケンコウサヌキ9,478(俊さん訂正)。伊藤友隆21,780は出金のため売上ではなく区分保留(要確認)</t>
+          <t>【販売手数料(マージン)】7月 107,158円=カ)ルフレ39,600＋アワノ36,300＋ケンコウサヌキ9,478＋伊藤友隆21,780(いずれも俊さん指定)</t>
         </is>
       </c>
       <c r="B38" s="6" t="n"/>
@@ -10235,7 +10291,7 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>【役員報酬】伊藤明日香30万で確定(俊さん確認済)</t>
+          <t>【三井住友 月末残】補助簿(口座開設6/17〜/伝票179-214)より。4-5月未開設=0、6月末≒0(▲1,005)、7月末163,569、8月末はWeb21実残11,973。通帳がない口座のため入出金から算定</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
@@ -10247,7 +10303,7 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>【方針計上済】役員報酬70万/月・地代家賃20万/月・旅費枠30万/月。実際の出金(仮払金)との精算(前渡→費用振替)は税理士で</t>
+          <t>【役員報酬】伊藤明日香30万で確定(俊さん確認済)</t>
         </is>
       </c>
       <c r="B40" s="6" t="n"/>
@@ -10259,7 +10315,7 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>【減価償却/繰延資産償却】0で計上(第1期の繰延資産償却1,063,398は第1期で終了と推定)。ソフトウェア残416,675の償却要否のみ税理士確認</t>
+          <t>【方針計上済】役員報酬70万/月・地代家賃20万/月・旅費枠30万/月。実際の出金(仮払金)との精算(前渡→費用振替)は税理士で</t>
         </is>
       </c>
       <c r="B41" s="6" t="n"/>
@@ -10271,7 +10327,7 @@
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>【現預金】京信・三井住友の2行のみ(他口座なし・俊さん確認済)。京信の月末残は確定。三井住友の各月末残の取得要(BS現預金を2行合算で確定するため)</t>
+          <t>【減価償却/繰延資産償却】0で計上(第1期の繰延資産償却1,063,398は第1期で終了と推定)。ソフトウェア残416,675の償却要否のみ税理士確認</t>
         </is>
       </c>
       <c r="B42" s="6" t="n"/>
@@ -10283,7 +10339,7 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>立替経費(山中)：7・8月のレシート未取込</t>
+          <t>【現預金】京信・三井住友の2行のみ(他口座なし・俊さん確認済)。京信の月末残は確定。三井住友の各月末残の取得要(BS現預金を2行合算で確定するため)</t>
         </is>
       </c>
       <c r="B43" s="6" t="n"/>
@@ -10295,7 +10351,7 @@
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>資本金：現金増資(京信タグ3,000,000＋区分反映426,000)＋現物出資(4/20 8,400,000・4/30 4,230,000)の整理要</t>
+          <t>立替経費(山中)：7・8月のレシート未取込</t>
         </is>
       </c>
       <c r="B44" s="6" t="n"/>
@@ -10304,8 +10360,20 @@
       <c r="E44" s="6" t="n"/>
       <c r="F44" s="7" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>資本金：現金増資(京信タグ3,000,000＋区分反映426,000)＋現物出資(4/20 8,400,000・4/30 4,230,000)の整理要</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A42:F42"/>
@@ -10313,6 +10381,7 @@
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A39:F39"/>

--- a/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/月次決算/電子CB農法_月次試算表_第2期2026年4-8月.xlsx
@@ -1268,10 +1268,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>82365</v>
+        <v>82935</v>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
         <v>6600</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>6600</v>
+        <v>13200</v>
       </c>
       <c r="H21" s="15" t="inlineStr"/>
     </row>
@@ -1587,7 +1587,7 @@
         <v>13240</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>5880</v>
+        <v>6025</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>3585</v>
@@ -1596,10 +1596,10 @@
         <v>9310</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1245</v>
+        <v>1975</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>33260</v>
+        <v>34135</v>
       </c>
       <c r="H23" s="15" t="inlineStr"/>
     </row>
@@ -1613,7 +1613,7 @@
         <v>1407809</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1438840</v>
+        <v>1438985</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>1310399</v>
@@ -1622,10 +1622,10 @@
         <v>2202571</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1201245</v>
+        <v>1209145</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>7560864</v>
+        <v>7568909</v>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>-1372489</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>-1138985</v>
+        <v>-1139130</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>-1217334</v>
@@ -1652,10 +1652,10 @@
         <v>-2162320</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>-1201245</v>
+        <v>-1209145</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>-7092373</v>
+        <v>-7100418</v>
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
@@ -1696,10 +1696,10 @@
         <v>550165</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>550165</v>
+        <v>750165</v>
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0</v>
+        <v>34717</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>10000</v>
@@ -1726,10 +1726,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>10000</v>
+        <v>64717</v>
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
@@ -1841,14 +1841,14 @@
         <v>60909</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>607021</v>
+        <v>443452</v>
       </c>
       <c r="G3" s="11" t="n">
         <v>323397</v>
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>2行合算。京信=通帳一致。三井住友=補助簿(口座開設6/17〜/4-5月未開設・6月末≒0)＋8月末Web21実残¥11,973</t>
+          <t>2行合算(他口座なし)。京信=通帳一致。三井住友は8月末¥11,973のみ確定・4〜7月末は未取得明細により未確定(暫定＝京信のみ)</t>
         </is>
       </c>
     </row>
@@ -1887,24 +1887,16 @@
         </is>
       </c>
       <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>163569</v>
-      </c>
+      <c r="C5" s="16" t="inlineStr"/>
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="16" t="inlineStr"/>
+      <c r="F5" s="16" t="inlineStr"/>
       <c r="G5" s="11" t="n">
         <v>11973</v>
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>口座開設6/17〜。6月末は口座ほぼ空(▲1,005/概算0)</t>
+          <t>8月末¥11,973（Web21実残）。4〜7月末は未取得明細により要確認</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2134,7 @@
         <v>2978986</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>36000</v>
+        <v>336000</v>
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
@@ -7648,7 +7640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7720,40 +7712,34 @@
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="n">
-        <v>179</v>
-      </c>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="n"/>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>現金</t>
+          <t>振替(資金移動)</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr"/>
       <c r="E3" s="11" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="F3" s="11" t="inlineStr"/>
-      <c r="G3" s="11" t="n">
-        <v>100000</v>
-      </c>
+      <c r="G3" s="11" t="inlineStr"/>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ</t>
+          <t>京信5/1提携ネットより振替入金（資金移動・突合確認）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="n">
-        <v>180</v>
-      </c>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n"/>
       <c r="C4" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
@@ -7762,193 +7748,171 @@
       <c r="D4" s="10" t="inlineStr"/>
       <c r="E4" s="11" t="inlineStr"/>
       <c r="F4" s="11" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>0</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="G4" s="11" t="inlineStr"/>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>W21 ﾕ)ｶｹﾊｼ</t>
+          <t>アプリ明細(摘要非表示)要確認</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>181</v>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="11" t="inlineStr"/>
       <c r="F5" s="11" t="n">
-        <v>145</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>-145</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="G5" s="11" t="inlineStr"/>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>アプリ明細(摘要非表示)要確認</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>182</v>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>通信費</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr"/>
       <c r="E6" s="11" t="inlineStr"/>
       <c r="F6" s="11" t="n">
-        <v>430</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>-575</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="G6" s="11" t="inlineStr"/>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+          <t>アプリ明細(摘要非表示)要確認</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="n">
-        <v>183</v>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>通信費</t>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr"/>
       <c r="E7" s="11" t="inlineStr"/>
       <c r="F7" s="11" t="n">
-        <v>430</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>-1005</v>
-      </c>
+        <v>22407</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr"/>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+          <t>アプリ明細(摘要非表示)要確認</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>184</v>
-      </c>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n"/>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr"/>
       <c r="E8" s="11" t="inlineStr"/>
       <c r="F8" s="11" t="n">
-        <v>430</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>-1435</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="G8" s="11" t="inlineStr"/>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+          <t>アプリ明細(摘要非表示)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="n">
-        <v>185</v>
-      </c>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n"/>
       <c r="C9" s="16" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr"/>
-      <c r="E9" s="11" t="n">
-        <v>145</v>
-      </c>
-      <c r="F9" s="11" t="inlineStr"/>
-      <c r="G9" s="11" t="n">
-        <v>-1290</v>
-      </c>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="11" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr"/>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐ</t>
+          <t>アプリ明細(摘要非表示・5月計上)要確認</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B10" s="18" t="n">
-        <v>186</v>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>179</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>現金</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr"/>
       <c r="E10" s="11" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="F10" s="11" t="inlineStr"/>
       <c r="G10" s="11" t="n">
-        <v>48710</v>
+        <v>100000</v>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐ</t>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B11" s="18" t="n">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
@@ -7956,27 +7920,27 @@
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr"/>
-      <c r="E11" s="11" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F11" s="11" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="n">
+        <v>100000</v>
+      </c>
       <c r="G11" s="11" t="n">
-        <v>548710</v>
+        <v>0</v>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ｾﾌﾞﾝBK05KJ</t>
+          <t>W21 ﾕ)ｶｹﾊｼ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B12" s="18" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
@@ -7986,137 +7950,137 @@
       <c r="D12" s="10" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr"/>
       <c r="F12" s="11" t="n">
-        <v>330</v>
+        <v>145</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>548380</v>
+        <v>-145</v>
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>ｶ-ﾄﾞﾃｽｳﾘﾖｳ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>189</v>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>182</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>通信費</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr"/>
       <c r="E13" s="11" t="inlineStr"/>
       <c r="F13" s="11" t="n">
-        <v>90300</v>
+        <v>430</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>458080</v>
+        <v>-575</v>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>W21 ﾕ)ｶｹﾊｼ</t>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>支払手数料</t>
+          <t>通信費</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr"/>
       <c r="E14" s="11" t="inlineStr"/>
       <c r="F14" s="11" t="n">
-        <v>145</v>
+        <v>430</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>457935</v>
+        <v>-1005</v>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>支払報酬料</t>
+          <t>通信費</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
       <c r="E15" s="11" t="inlineStr"/>
       <c r="F15" s="11" t="n">
-        <v>149685</v>
+        <v>430</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>308250</v>
+        <v>-1435</v>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>W21 ﾂｼﾞ ﾏｻｼ</t>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>192</v>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>185</v>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="11" t="inlineStr"/>
-      <c r="F16" s="11" t="n">
+      <c r="E16" s="11" t="n">
         <v>145</v>
       </c>
+      <c r="F16" s="11" t="inlineStr"/>
       <c r="G16" s="11" t="n">
-        <v>308105</v>
+        <v>-1290</v>
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>ﾌﾘｺﾐ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
@@ -8124,192 +8088,184 @@
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="11" t="inlineStr"/>
-      <c r="F17" s="11" t="n">
-        <v>70000</v>
-      </c>
+      <c r="E17" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F17" s="11" t="inlineStr"/>
       <c r="G17" s="11" t="n">
-        <v>238105</v>
+        <v>48710</v>
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>W21 ﾐﾗﾊﾟ</t>
+          <t>ﾌﾘｺﾐ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>194</v>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>187</v>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="11" t="inlineStr"/>
-      <c r="F18" s="11" t="n">
-        <v>145</v>
-      </c>
+      <c r="E18" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F18" s="11" t="inlineStr"/>
       <c r="G18" s="11" t="n">
-        <v>237960</v>
+        <v>548710</v>
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ｾﾌﾞﾝBK05KJ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>195</v>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>188</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
       <c r="E19" s="11" t="inlineStr"/>
       <c r="F19" s="11" t="n">
-        <v>6600</v>
+        <v>330</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>231360</v>
+        <v>548380</v>
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>W21 ﾄﾞ)ﾄﾞｼﾞﾖｳｼﾝﾀﾞﾝﾖｳ</t>
+          <t>ｶ-ﾄﾞﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>196</v>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>189</v>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
       <c r="E20" s="11" t="inlineStr"/>
       <c r="F20" s="11" t="n">
-        <v>145</v>
+        <v>90300</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>231215</v>
+        <v>458080</v>
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ﾕ)ｶｹﾊｼ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" s="18" t="n">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
       <c r="E21" s="11" t="inlineStr"/>
       <c r="F21" s="11" t="n">
-        <v>13120</v>
+        <v>145</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>218095</v>
+        <v>457935</v>
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>仮払金</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>イトウアスカ</t>
-        </is>
-      </c>
+          <t>支払報酬料</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
       <c r="E22" s="11" t="inlineStr"/>
       <c r="F22" s="11" t="n">
-        <v>11077</v>
+        <v>149685</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>207018</v>
+        <v>308250</v>
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>W21 ｲﾄｳ ｱｽｶ</t>
+          <t>W21 ﾂｼﾞ ﾏｻｼ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" s="18" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>仮払金</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>イトウアスカ</t>
-        </is>
-      </c>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
       <c r="E23" s="11" t="inlineStr"/>
       <c r="F23" s="11" t="n">
-        <v>5909</v>
+        <v>145</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>201109</v>
+        <v>308105</v>
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>W21 ｲﾄｳ ｱｽｶ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -8320,67 +8276,63 @@
         </is>
       </c>
       <c r="B24" s="18" t="n">
-        <v>200</v>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>仮払金</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>イトウアスカ</t>
-        </is>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
       <c r="E24" s="11" t="inlineStr"/>
       <c r="F24" s="11" t="n">
-        <v>10000</v>
+        <v>70000</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>191109</v>
+        <v>238105</v>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>W21 ｲﾄｳ ｱｽｶ</t>
+          <t>W21 ﾐﾗﾊﾟ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" s="18" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
       <c r="E25" s="11" t="inlineStr"/>
       <c r="F25" s="11" t="n">
-        <v>1960</v>
+        <v>145</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>189149</v>
+        <v>237960</v>
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
@@ -8390,81 +8342,81 @@
       <c r="D26" s="10" t="inlineStr"/>
       <c r="E26" s="11" t="inlineStr"/>
       <c r="F26" s="11" t="n">
-        <v>150000</v>
+        <v>6600</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>39149</v>
+        <v>231360</v>
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>W21 ｺｳﾍﾞﾁｻﾞｲｺﾞｳﾄﾞｳｼﾞ</t>
+          <t>W21 ﾄﾞ)ﾄﾞｼﾞﾖｳｼﾝﾀﾞﾝﾖｳ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" s="18" t="n">
-        <v>203</v>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>196</v>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="11" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr"/>
+      <c r="F27" s="11" t="n">
+        <v>145</v>
+      </c>
       <c r="G27" s="11" t="n">
-        <v>539149</v>
+        <v>231215</v>
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B28" s="18" t="n">
-        <v>204</v>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>197</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>通信費</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="11" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F28" s="11" t="inlineStr"/>
+      <c r="E28" s="11" t="inlineStr"/>
+      <c r="F28" s="11" t="n">
+        <v>13120</v>
+      </c>
       <c r="G28" s="11" t="n">
-        <v>1039149</v>
+        <v>218095</v>
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -8478,10 +8430,10 @@
       </c>
       <c r="E29" s="11" t="inlineStr"/>
       <c r="F29" s="11" t="n">
-        <v>200000</v>
+        <v>11077</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>839149</v>
+        <v>207018</v>
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
@@ -8492,39 +8444,43 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr"/>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
       <c r="E30" s="11" t="inlineStr"/>
       <c r="F30" s="11" t="n">
-        <v>145</v>
+        <v>5909</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>839004</v>
+        <v>201109</v>
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B31" s="18" t="n">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -8538,10 +8494,10 @@
       </c>
       <c r="E31" s="11" t="inlineStr"/>
       <c r="F31" s="11" t="n">
-        <v>300000</v>
+        <v>10000</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>539004</v>
+        <v>191109</v>
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
@@ -8556,24 +8512,24 @@
         </is>
       </c>
       <c r="B32" s="18" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>支払手数料</t>
+          <t>通信費</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
       <c r="E32" s="11" t="inlineStr"/>
       <c r="F32" s="11" t="n">
-        <v>145</v>
+        <v>1960</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>538859</v>
+        <v>189149</v>
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8540,7 @@
         </is>
       </c>
       <c r="B33" s="18" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
@@ -8594,14 +8550,14 @@
       <c r="D33" s="10" t="inlineStr"/>
       <c r="E33" s="11" t="inlineStr"/>
       <c r="F33" s="11" t="n">
-        <v>275000</v>
+        <v>150000</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>263859</v>
+        <v>39149</v>
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>W21 ｶ.ｱﾙｹﾐｱｺﾈｸﾄ</t>
+          <t>W21 ｺｳﾍﾞﾁｻﾞｲｺﾞｳﾄﾞｳｼﾞ</t>
         </is>
       </c>
     </row>
@@ -8612,35 +8568,35 @@
         </is>
       </c>
       <c r="B34" s="18" t="n">
-        <v>210</v>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>203</v>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
-      <c r="E34" s="11" t="inlineStr"/>
-      <c r="F34" s="11" t="n">
-        <v>145</v>
-      </c>
+      <c r="E34" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
       <c r="G34" s="11" t="n">
-        <v>263714</v>
+        <v>539149</v>
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
@@ -8648,104 +8604,600 @@
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="11" t="inlineStr"/>
-      <c r="F35" s="11" t="n">
-        <v>100000</v>
-      </c>
+      <c r="E35" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="n">
-        <v>163714</v>
+        <v>1039149</v>
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>W21 ｶ.ｷｼﾕｳﾌﾟﾗﾂﾄﾌｵ-ﾑ</t>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B36" s="18" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr"/>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
       <c r="E36" s="11" t="inlineStr"/>
       <c r="F36" s="11" t="n">
-        <v>145</v>
+        <v>200000</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>163569</v>
+        <v>839149</v>
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B37" s="18" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>仮払金</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>イトウアスカ</t>
-        </is>
-      </c>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr"/>
       <c r="E37" s="11" t="inlineStr"/>
       <c r="F37" s="11" t="n">
-        <v>36000</v>
+        <v>145</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>127569</v>
+        <v>839004</v>
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>W21 ｲﾄｳ ｱｽｶ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" s="18" t="n">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr"/>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
       <c r="E38" s="11" t="inlineStr"/>
       <c r="F38" s="11" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>539004</v>
+      </c>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="n">
+        <v>208</v>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr"/>
+      <c r="E39" s="11" t="inlineStr"/>
+      <c r="F39" s="11" t="n">
         <v>145</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G39" s="11" t="n">
+        <v>538859</v>
+      </c>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n">
+        <v>209</v>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr"/>
+      <c r="E40" s="11" t="inlineStr"/>
+      <c r="F40" s="11" t="n">
+        <v>275000</v>
+      </c>
+      <c r="G40" s="11" t="n">
+        <v>263859</v>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>W21 ｶ.ｱﾙｹﾐｱｺﾈｸﾄ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="n">
+        <v>210</v>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr"/>
+      <c r="E41" s="11" t="inlineStr"/>
+      <c r="F41" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>263714</v>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="n">
+        <v>211</v>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr"/>
+      <c r="E42" s="11" t="inlineStr"/>
+      <c r="F42" s="11" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G42" s="11" t="n">
+        <v>163714</v>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>W21 ｶ.ｷｼﾕｳﾌﾟﾗﾂﾄﾌｵ-ﾑ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="n">
+        <v>212</v>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr"/>
+      <c r="E43" s="11" t="inlineStr"/>
+      <c r="F43" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>163569</v>
+      </c>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="n">
+        <v>213</v>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr"/>
+      <c r="F44" s="11" t="n">
+        <v>36000</v>
+      </c>
+      <c r="G44" s="11" t="n">
+        <v>127569</v>
+      </c>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n">
+        <v>214</v>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr"/>
+      <c r="E45" s="11" t="inlineStr"/>
+      <c r="F45" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="G45" s="11" t="n">
         <v>127424</v>
       </c>
-      <c r="H38" s="15" t="inlineStr">
+      <c r="H45" s="15" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>消耗品費</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr"/>
+      <c r="E46" s="11" t="inlineStr"/>
+      <c r="F46" s="11" t="n">
+        <v>570</v>
+      </c>
+      <c r="G46" s="11" t="inlineStr"/>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>W21 カ)モノタロウ ※科目要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr"/>
+      <c r="E47" s="11" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F47" s="11" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr"/>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>キャッシュカード セブンBK06UF（入金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr"/>
+      <c r="E48" s="11" t="inlineStr"/>
+      <c r="F48" s="11" t="n">
+        <v>220</v>
+      </c>
+      <c r="G48" s="11" t="inlineStr"/>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>カードテスウリョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr"/>
+      <c r="F49" s="11" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G49" s="11" t="inlineStr"/>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>W21 イトウ アスカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr"/>
+      <c r="E50" s="11" t="inlineStr"/>
+      <c r="F50" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="G50" s="11" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>フリコミテスウリョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>受取利息</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr"/>
+      <c r="E51" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="F51" s="11" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr"/>
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>普通預金利息</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>研究開発費</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr"/>
+      <c r="E52" s="11" t="inlineStr"/>
+      <c r="F52" s="11" t="n">
+        <v>6600</v>
+      </c>
+      <c r="G52" s="11" t="inlineStr"/>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>W21 ド)ドジョウシンダンヨウ（7/24分と別取引）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr"/>
+      <c r="E53" s="11" t="inlineStr"/>
+      <c r="F53" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="G53" s="11" t="inlineStr"/>
+      <c r="H53" s="15" t="inlineStr">
+        <is>
+          <t>フリコミテスウリョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>雑収入</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr"/>
+      <c r="E54" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="F54" s="11" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr"/>
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>SMBC 手数料キャッシュバック</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr"/>
+      <c r="E55" s="11" t="inlineStr"/>
+      <c r="F55" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G55" s="11" t="inlineStr"/>
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>キャッシュカード セブンBK0Q5T（現金引出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="n"/>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr"/>
+      <c r="E56" s="11" t="inlineStr"/>
+      <c r="F56" s="11" t="n">
+        <v>220</v>
+      </c>
+      <c r="G56" s="11" t="inlineStr"/>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>カードテスウリョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>雑収入</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr"/>
+      <c r="E57" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F57" s="11" t="inlineStr"/>
+      <c r="G57" s="11" t="inlineStr"/>
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>SMBC テスウリョウ返金</t>
         </is>
       </c>
     </row>
